--- a/Industry Visit - Member Tracking (1).xlsx
+++ b/Industry Visit - Member Tracking (1).xlsx
@@ -20,7 +20,7 @@
     <sheet name="IFS" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="Zone24x7" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="Cambio" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="Lion Beer" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="Lion Brewery" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Atlas Labs'!$A$1:$E$25</definedName>
@@ -37,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <color rgb="FF000000"/>
@@ -223,8 +223,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill/>
     </fill>
@@ -387,6 +393,12 @@
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F497D"/>
+        <bgColor rgb="001F497D"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="9">
     <border/>
@@ -474,7 +486,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -738,6 +750,12 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="28" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10216,9 +10234,395 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15.75" customHeight="1"/>
-  <sheetData/>
+  <cols>
+    <col width="32" customWidth="1" style="108" min="1" max="1"/>
+    <col width="48" customWidth="1" style="108" min="2" max="2"/>
+    <col width="15" customWidth="1" style="108" min="3" max="3"/>
+    <col width="16" customWidth="1" style="108" min="4" max="4"/>
+    <col width="33" customWidth="1" style="108" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="115" t="inlineStr">
+        <is>
+          <t>Full Name</t>
+        </is>
+      </c>
+      <c r="B1" s="115" t="inlineStr">
+        <is>
+          <t>IEEE Membership No</t>
+        </is>
+      </c>
+      <c r="C1" s="115" t="inlineStr">
+        <is>
+          <t>NIC</t>
+        </is>
+      </c>
+      <c r="D1" s="115" t="inlineStr">
+        <is>
+          <t>Phone Number</t>
+        </is>
+      </c>
+      <c r="E1" s="115" t="inlineStr">
+        <is>
+          <t>Email Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Chalani Rashmika Jayawickrama</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>I am a volunteer for graduation days at sliit</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>200170903253</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0775669478</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>rchalani50@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Roneth Asvin Galappaththi</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Battle Arena</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>200420800409</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0764215348</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>asvinroneth@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RAJAPAKSE RGRN</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>IEEE Day</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>200401500469</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>0767801400</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>rakindu.nenitha@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Haris Ali Isthihar Ali</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Battle Arena</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>200405110581</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>0758426130</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>isthimien@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Harshitha Yasiru</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Odyssey, cast 360</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>200524303750</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0770371157</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>harshithayasiru34@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Vihara Yasassrini Pathirana</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Secretary Team member - BioforgeX 26</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>200454810460</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>0766020082</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>hs26510421@my.sliit.lk</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Athiga Paunanthie</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>200550600032</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>0772866239</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>athigapaunanthie@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H. N. Manith Dulnim</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>200315913512</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>0712298959</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>hn.manithdulnimacc.1@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tharushi Wijesiriwardhana</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>200466703854</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>+94 743700501</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>en26300162@my.sliit.lk</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Rathnapala p.d.b</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>200118703605</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>0714181172</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>en23772472@my.sliit.lk</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Haazim Fazal</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>200513000950</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0764400982</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>haazimfazal7@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Ishodya Nimnadi Punchihewa</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>200564004096</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0769972699</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>it25101416@my.sliit.lk</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Senavirathna D.K.G.V.R.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>200429904370</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0763846657</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>vishwa18556@gmail.com</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -26811,7 +27215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N251"/>
+  <dimension ref="A1:O264"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="28" customWidth="1" style="108" min="1" max="1"/>
@@ -26896,6 +27300,11 @@
           <t>Cambio</t>
         </is>
       </c>
+      <c r="O1" s="109" t="inlineStr">
+        <is>
+          <t>Lion Brewery</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1" ht="22.5" customHeight="1" s="108">
       <c r="A2" s="103" t="inlineStr">
@@ -36519,6 +36928,474 @@
         <v/>
       </c>
       <c r="N251" s="111" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Chalani Rashmika Jayawickrama</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>200170903253</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>I am a volunteer for graduation days at sliit</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>0775669478</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>rchalani50@gmail.com</t>
+        </is>
+      </c>
+      <c r="F252" s="114">
+        <f>COUNTIF(G252:O252,"Y")</f>
+        <v/>
+      </c>
+      <c r="O252" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Roneth Asvin Galappaththi</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>200420800409</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Battle Arena</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>0764215348</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>asvinroneth@gmail.com</t>
+        </is>
+      </c>
+      <c r="F253" s="114">
+        <f>COUNTIF(G253:O253,"Y")</f>
+        <v/>
+      </c>
+      <c r="O253" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>RAJAPAKSE RGRN</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>200401500469</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>IEEE Day</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>0767801400</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>rakindu.nenitha@gmail.com</t>
+        </is>
+      </c>
+      <c r="F254" s="114">
+        <f>COUNTIF(G254:O254,"Y")</f>
+        <v/>
+      </c>
+      <c r="O254" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Haris Ali Isthihar Ali</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>200405110581</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Battle Arena</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>0758426130</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>isthimien@gmail.com</t>
+        </is>
+      </c>
+      <c r="F255" s="114">
+        <f>COUNTIF(G255:O255,"Y")</f>
+        <v/>
+      </c>
+      <c r="O255" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Harshitha Yasiru</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>200524303750</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Odyssey, cast 360</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0770371157</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>harshithayasiru34@gmail.com</t>
+        </is>
+      </c>
+      <c r="F256" s="114">
+        <f>COUNTIF(G256:O256,"Y")</f>
+        <v/>
+      </c>
+      <c r="O256" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Vihara Yasassrini Pathirana</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>200454810460</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Secretary Team member - BioforgeX 26</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>0766020082</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>hs26510421@my.sliit.lk</t>
+        </is>
+      </c>
+      <c r="F257" s="114">
+        <f>COUNTIF(G257:O257,"Y")</f>
+        <v/>
+      </c>
+      <c r="O257" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Athiga Paunanthie</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>200550600032</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>0772866239</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>athigapaunanthie@gmail.com</t>
+        </is>
+      </c>
+      <c r="F258" s="114">
+        <f>COUNTIF(G258:O258,"Y")</f>
+        <v/>
+      </c>
+      <c r="O258" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>H. N. Manith Dulnim</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>200315913512</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>0712298959</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>hn.manithdulnimacc.1@gmail.com</t>
+        </is>
+      </c>
+      <c r="F259" s="114">
+        <f>COUNTIF(G259:O259,"Y")</f>
+        <v/>
+      </c>
+      <c r="O259" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>Tharushi Wijesiriwardhana</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>200466703854</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>+94 743700501</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>en26300162@my.sliit.lk</t>
+        </is>
+      </c>
+      <c r="F260" s="114">
+        <f>COUNTIF(G260:O260,"Y")</f>
+        <v/>
+      </c>
+      <c r="O260" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Rathnapala p.d.b</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>200118703605</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>0714181172</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>en23772472@my.sliit.lk</t>
+        </is>
+      </c>
+      <c r="F261" s="114">
+        <f>COUNTIF(G261:O261,"Y")</f>
+        <v/>
+      </c>
+      <c r="O261" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Haazim Fazal</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>200513000950</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>0764400982</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>haazimfazal7@gmail.com</t>
+        </is>
+      </c>
+      <c r="F262" s="114">
+        <f>COUNTIF(G262:O262,"Y")</f>
+        <v/>
+      </c>
+      <c r="O262" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Ishodya Nimnadi Punchihewa</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>200564004096</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>0769972699</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>it25101416@my.sliit.lk</t>
+        </is>
+      </c>
+      <c r="F263" s="114">
+        <f>COUNTIF(G263:O263,"Y")</f>
+        <v/>
+      </c>
+      <c r="O263" s="114" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Senavirathna D.K.G.V.R.</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>200429904370</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>0763846657</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>vishwa18556@gmail.com</t>
+        </is>
+      </c>
+      <c r="F264" s="114">
+        <f>COUNTIF(G264:O264,"Y")</f>
+        <v/>
+      </c>
+      <c r="O264" s="114" t="inlineStr">
         <is>
           <t>Y</t>
         </is>

--- a/Industry Visit - Member Tracking (1).xlsx
+++ b/Industry Visit - Member Tracking (1).xlsx
@@ -10272,351 +10272,299 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>Chalani Rashmika Jayawickrama</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>I am a volunteer for graduation days at sliit</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="B2" s="0" t="n"/>
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>200170903253</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>0775669478</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>rchalani50@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>Roneth Asvin Galappaththi</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Battle Arena</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="B3" s="0" t="n"/>
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>200420800409</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>0764215348</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>asvinroneth@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>RAJAPAKSE RGRN</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>IEEE Day</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="B4" s="0" t="n"/>
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>200401500469</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>0767801400</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>rakindu.nenitha@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>Haris Ali Isthihar Ali</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Battle Arena</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="B5" s="0" t="n"/>
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>200405110581</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>0758426130</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>isthimien@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>Harshitha Yasiru</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Odyssey, cast 360</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="B6" s="0" t="n"/>
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>200524303750</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>0770371157</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>harshithayasiru34@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>Vihara Yasassrini Pathirana</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Secretary Team member - BioforgeX 26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B7" s="0" t="n"/>
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>200454810460</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>0766020082</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>hs26510421@my.sliit.lk</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>Athiga Paunanthie</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="0" t="n"/>
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>200550600032</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>0772866239</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>athigapaunanthie@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>H. N. Manith Dulnim</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="0" t="n"/>
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>200315913512</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>0712298959</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>hn.manithdulnimacc.1@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>Tharushi Wijesiriwardhana</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="0" t="n"/>
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>200466703854</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>+94 743700501</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>en26300162@my.sliit.lk</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>Rathnapala p.d.b</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B11" s="0" t="n"/>
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>200118703605</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>0714181172</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>en23772472@my.sliit.lk</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>Haazim Fazal</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B12" s="0" t="n"/>
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>200513000950</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>0764400982</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>haazimfazal7@gmail.com</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>Ishodya Nimnadi Punchihewa</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="B13" s="0" t="n"/>
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>200564004096</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>0769972699</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>it25101416@my.sliit.lk</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>Senavirathna D.K.G.V.R.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B14" s="0" t="n"/>
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>200429904370</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>0763846657</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>vishwa18556@gmail.com</t>
         </is>
@@ -36934,27 +36882,23 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
+      <c r="A252" s="0" t="inlineStr">
         <is>
           <t>Chalani Rashmika Jayawickrama</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B252" s="0" t="inlineStr">
         <is>
           <t>200170903253</t>
         </is>
       </c>
-      <c r="C252" t="inlineStr">
-        <is>
-          <t>I am a volunteer for graduation days at sliit</t>
-        </is>
-      </c>
-      <c r="D252" t="inlineStr">
+      <c r="C252" s="0" t="n"/>
+      <c r="D252" s="0" t="inlineStr">
         <is>
           <t>0775669478</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E252" s="0" t="inlineStr">
         <is>
           <t>rchalani50@gmail.com</t>
         </is>
@@ -36970,27 +36914,23 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr">
+      <c r="A253" s="0" t="inlineStr">
         <is>
           <t>Roneth Asvin Galappaththi</t>
         </is>
       </c>
-      <c r="B253" t="inlineStr">
+      <c r="B253" s="0" t="inlineStr">
         <is>
           <t>200420800409</t>
         </is>
       </c>
-      <c r="C253" t="inlineStr">
-        <is>
-          <t>Battle Arena</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
+      <c r="C253" s="0" t="n"/>
+      <c r="D253" s="0" t="inlineStr">
         <is>
           <t>0764215348</t>
         </is>
       </c>
-      <c r="E253" t="inlineStr">
+      <c r="E253" s="0" t="inlineStr">
         <is>
           <t>asvinroneth@gmail.com</t>
         </is>
@@ -37006,27 +36946,23 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
+      <c r="A254" s="0" t="inlineStr">
         <is>
           <t>RAJAPAKSE RGRN</t>
         </is>
       </c>
-      <c r="B254" t="inlineStr">
+      <c r="B254" s="0" t="inlineStr">
         <is>
           <t>200401500469</t>
         </is>
       </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>IEEE Day</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
+      <c r="C254" s="0" t="n"/>
+      <c r="D254" s="0" t="inlineStr">
         <is>
           <t>0767801400</t>
         </is>
       </c>
-      <c r="E254" t="inlineStr">
+      <c r="E254" s="0" t="inlineStr">
         <is>
           <t>rakindu.nenitha@gmail.com</t>
         </is>
@@ -37042,27 +36978,23 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr">
+      <c r="A255" s="0" t="inlineStr">
         <is>
           <t>Haris Ali Isthihar Ali</t>
         </is>
       </c>
-      <c r="B255" t="inlineStr">
+      <c r="B255" s="0" t="inlineStr">
         <is>
           <t>200405110581</t>
         </is>
       </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>Battle Arena</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
+      <c r="C255" s="0" t="n"/>
+      <c r="D255" s="0" t="inlineStr">
         <is>
           <t>0758426130</t>
         </is>
       </c>
-      <c r="E255" t="inlineStr">
+      <c r="E255" s="0" t="inlineStr">
         <is>
           <t>isthimien@gmail.com</t>
         </is>
@@ -37078,27 +37010,23 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr">
+      <c r="A256" s="0" t="inlineStr">
         <is>
           <t>Harshitha Yasiru</t>
         </is>
       </c>
-      <c r="B256" t="inlineStr">
+      <c r="B256" s="0" t="inlineStr">
         <is>
           <t>200524303750</t>
         </is>
       </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>Odyssey, cast 360</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
+      <c r="C256" s="0" t="n"/>
+      <c r="D256" s="0" t="inlineStr">
         <is>
           <t>0770371157</t>
         </is>
       </c>
-      <c r="E256" t="inlineStr">
+      <c r="E256" s="0" t="inlineStr">
         <is>
           <t>harshithayasiru34@gmail.com</t>
         </is>
@@ -37114,27 +37042,23 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr">
+      <c r="A257" s="0" t="inlineStr">
         <is>
           <t>Vihara Yasassrini Pathirana</t>
         </is>
       </c>
-      <c r="B257" t="inlineStr">
+      <c r="B257" s="0" t="inlineStr">
         <is>
           <t>200454810460</t>
         </is>
       </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>Secretary Team member - BioforgeX 26</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
+      <c r="C257" s="0" t="n"/>
+      <c r="D257" s="0" t="inlineStr">
         <is>
           <t>0766020082</t>
         </is>
       </c>
-      <c r="E257" t="inlineStr">
+      <c r="E257" s="0" t="inlineStr">
         <is>
           <t>hs26510421@my.sliit.lk</t>
         </is>
@@ -37150,27 +37074,23 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr">
+      <c r="A258" s="0" t="inlineStr">
         <is>
           <t>Athiga Paunanthie</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B258" s="0" t="inlineStr">
         <is>
           <t>200550600032</t>
         </is>
       </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr">
+      <c r="C258" s="0" t="n"/>
+      <c r="D258" s="0" t="inlineStr">
         <is>
           <t>0772866239</t>
         </is>
       </c>
-      <c r="E258" t="inlineStr">
+      <c r="E258" s="0" t="inlineStr">
         <is>
           <t>athigapaunanthie@gmail.com</t>
         </is>
@@ -37186,27 +37106,23 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
+      <c r="A259" s="0" t="inlineStr">
         <is>
           <t>H. N. Manith Dulnim</t>
         </is>
       </c>
-      <c r="B259" t="inlineStr">
+      <c r="B259" s="0" t="inlineStr">
         <is>
           <t>200315913512</t>
         </is>
       </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
+      <c r="C259" s="0" t="n"/>
+      <c r="D259" s="0" t="inlineStr">
         <is>
           <t>0712298959</t>
         </is>
       </c>
-      <c r="E259" t="inlineStr">
+      <c r="E259" s="0" t="inlineStr">
         <is>
           <t>hn.manithdulnimacc.1@gmail.com</t>
         </is>
@@ -37222,27 +37138,23 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
+      <c r="A260" s="0" t="inlineStr">
         <is>
           <t>Tharushi Wijesiriwardhana</t>
         </is>
       </c>
-      <c r="B260" t="inlineStr">
+      <c r="B260" s="0" t="inlineStr">
         <is>
           <t>200466703854</t>
         </is>
       </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D260" t="inlineStr">
+      <c r="C260" s="0" t="n"/>
+      <c r="D260" s="0" t="inlineStr">
         <is>
           <t>+94 743700501</t>
         </is>
       </c>
-      <c r="E260" t="inlineStr">
+      <c r="E260" s="0" t="inlineStr">
         <is>
           <t>en26300162@my.sliit.lk</t>
         </is>
@@ -37258,27 +37170,23 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
+      <c r="A261" s="0" t="inlineStr">
         <is>
           <t>Rathnapala p.d.b</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B261" s="0" t="inlineStr">
         <is>
           <t>200118703605</t>
         </is>
       </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
+      <c r="C261" s="0" t="n"/>
+      <c r="D261" s="0" t="inlineStr">
         <is>
           <t>0714181172</t>
         </is>
       </c>
-      <c r="E261" t="inlineStr">
+      <c r="E261" s="0" t="inlineStr">
         <is>
           <t>en23772472@my.sliit.lk</t>
         </is>
@@ -37294,27 +37202,23 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
+      <c r="A262" s="0" t="inlineStr">
         <is>
           <t>Haazim Fazal</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B262" s="0" t="inlineStr">
         <is>
           <t>200513000950</t>
         </is>
       </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
+      <c r="C262" s="0" t="n"/>
+      <c r="D262" s="0" t="inlineStr">
         <is>
           <t>0764400982</t>
         </is>
       </c>
-      <c r="E262" t="inlineStr">
+      <c r="E262" s="0" t="inlineStr">
         <is>
           <t>haazimfazal7@gmail.com</t>
         </is>
@@ -37330,27 +37234,23 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
+      <c r="A263" s="0" t="inlineStr">
         <is>
           <t>Ishodya Nimnadi Punchihewa</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B263" s="0" t="inlineStr">
         <is>
           <t>200564004096</t>
         </is>
       </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D263" t="inlineStr">
+      <c r="C263" s="0" t="n"/>
+      <c r="D263" s="0" t="inlineStr">
         <is>
           <t>0769972699</t>
         </is>
       </c>
-      <c r="E263" t="inlineStr">
+      <c r="E263" s="0" t="inlineStr">
         <is>
           <t>it25101416@my.sliit.lk</t>
         </is>
@@ -37366,27 +37266,23 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
+      <c r="A264" s="0" t="inlineStr">
         <is>
           <t>Senavirathna D.K.G.V.R.</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B264" s="0" t="inlineStr">
         <is>
           <t>200429904370</t>
         </is>
       </c>
-      <c r="C264" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
+      <c r="C264" s="0" t="n"/>
+      <c r="D264" s="0" t="inlineStr">
         <is>
           <t>0763846657</t>
         </is>
       </c>
-      <c r="E264" t="inlineStr">
+      <c r="E264" s="0" t="inlineStr">
         <is>
           <t>vishwa18556@gmail.com</t>
         </is>
